--- a/data/trans_orig/P36BPD09_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69167</t>
+          <t>64844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50560</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104762</t>
+          <t>102577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246975</t>
+          <t>247545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312314</t>
+          <t>309171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186303</t>
+          <t>188338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229551</t>
+          <t>231137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>449189</t>
+          <t>454208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>527906</t>
+          <t>527440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51636</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106681</t>
+          <t>108766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49953</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88605</t>
+          <t>87153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>110080</t>
+          <t>111965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180420</t>
+          <t>179010</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>29295</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61647</t>
+          <t>62589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>24916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58993</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62207</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110269</t>
+          <t>111184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>254549</t>
+          <t>254288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>304092</t>
+          <t>304152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>335236</t>
+          <t>335358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>429025</t>
+          <t>423005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>606897</t>
+          <t>604384</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>717350</t>
+          <t>714939</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78922</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123609</t>
+          <t>123748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59350</t>
+          <t>62932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127250</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150710</t>
+          <t>155771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235770</t>
+          <t>238860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53323</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31229</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52145</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65457</t>
+          <t>64961</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99898</t>
+          <t>98097</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327031</t>
+          <t>325174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>374841</t>
+          <t>373402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>350932</t>
+          <t>352411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386944</t>
+          <t>389139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>691030</t>
+          <t>689725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>748128</t>
+          <t>746430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126070</t>
+          <t>126562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168927</t>
+          <t>170616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113748</t>
+          <t>113795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147081</t>
+          <t>146709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250621</t>
+          <t>249514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>302072</t>
+          <t>302240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>54474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>48438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98552</t>
+          <t>98901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186533</t>
+          <t>182530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>607639</t>
+          <t>603908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>363794</t>
+          <t>352217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>466320</t>
+          <t>469158</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>497557</t>
+          <t>555796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1041312</t>
+          <t>1046138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>234628</t>
+          <t>237141</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>683359</t>
+          <t>686856</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200898</t>
+          <t>200073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>313316</t>
+          <t>324122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>464497</t>
+          <t>459995</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1055602</t>
+          <t>986951</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>61,73%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32999</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56935</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>40640</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89917</t>
+          <t>89079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>322787</t>
+          <t>324937</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365805</t>
+          <t>367961</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>334541</t>
+          <t>335640</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>369483</t>
+          <t>369807</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>671470</t>
+          <t>668685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>726599</t>
+          <t>725730</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150596</t>
+          <t>151350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>192070</t>
+          <t>191897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146003</t>
+          <t>146844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>178885</t>
+          <t>180215</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>308966</t>
+          <t>310167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>359434</t>
+          <t>365476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29509</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38343</t>
+          <t>37337</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61102</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>223313</t>
+          <t>223184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>252622</t>
+          <t>251610</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>100746</t>
+          <t>104186</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>376879</t>
+          <t>375757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>256957</t>
+          <t>246042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>617667</t>
+          <t>619313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93565</t>
+          <t>94758</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121556</t>
+          <t>123148</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>195293</t>
+          <t>196658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>495924</t>
+          <t>492283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>298259</t>
+          <t>295869</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>687905</t>
+          <t>694479</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37010</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35667</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55234</t>
+          <t>55150</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160306</t>
+          <t>161317</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>186653</t>
+          <t>187605</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>240537</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>269008</t>
+          <t>269563</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>411102</t>
+          <t>411831</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>449567</t>
+          <t>451030</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79564</t>
+          <t>78493</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>104162</t>
+          <t>103234</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>127301</t>
+          <t>128175</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>156233</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>212752</t>
+          <t>212535</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>250230</t>
+          <t>249457</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>184945</t>
+          <t>179667</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>283277</t>
+          <t>276971</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>201327</t>
+          <t>199428</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>275251</t>
+          <t>277190</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>414824</t>
+          <t>417732</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>536823</t>
+          <t>537790</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4030,17 +4030,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2100565</t>
+          <t>2100566</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1641686</t>
+          <t>1627905</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2284010</t>
+          <t>2278571</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1828015</t>
+          <t>1812225</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2400044</t>
+          <t>2403435</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3776327</t>
+          <t>3717717</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4633761</t>
+          <t>4627011</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>916649</t>
+          <t>919853</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1649940</t>
+          <t>1629412</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>999172</t>
+          <t>997406</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1636689</t>
+          <t>1655952</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1968710</t>
+          <t>1974319</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2918186</t>
+          <t>2970747</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD09_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42273</t>
+          <t>47641</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>31421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64844</t>
+          <t>72845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34322</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>26338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76594</t>
+          <t>87875</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53212</t>
+          <t>64727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102577</t>
+          <t>117335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>280789</t>
+          <t>283438</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247545</t>
+          <t>251630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309171</t>
+          <t>309865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>209539</t>
+          <t>243644</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188338</t>
+          <t>216409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231137</t>
+          <t>265854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>490328</t>
+          <t>527083</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>454208</t>
+          <t>488123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>527440</t>
+          <t>562480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76925</t>
+          <t>76713</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>54196</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108766</t>
+          <t>107369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67756</t>
+          <t>77138</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48907</t>
+          <t>56789</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87153</t>
+          <t>98602</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>144681</t>
+          <t>153851</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111965</t>
+          <t>124078</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179010</t>
+          <t>189502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43306</t>
+          <t>51427</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>73204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43411</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>37757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59365</t>
+          <t>65911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>86717</t>
+          <t>102236</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60483</t>
+          <t>80459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111184</t>
+          <t>127072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>279969</t>
+          <t>309469</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>254288</t>
+          <t>280259</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>304152</t>
+          <t>335581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>366427</t>
+          <t>336170</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>335358</t>
+          <t>314296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>423005</t>
+          <t>358481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>646396</t>
+          <t>645639</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>604384</t>
+          <t>608190</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>714939</t>
+          <t>681605</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100272</t>
+          <t>115994</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>91493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123748</t>
+          <t>144631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>101666</t>
+          <t>114104</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>93185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126696</t>
+          <t>133839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>201938</t>
+          <t>230098</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155771</t>
+          <t>199818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>238860</t>
+          <t>264124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>63407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41321</t>
+          <t>48737</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>38986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53573</t>
+          <t>62973</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>80505</t>
+          <t>95886</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64961</t>
+          <t>77878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>116094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>351620</t>
+          <t>399593</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>325174</t>
+          <t>374600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373402</t>
+          <t>425447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>369890</t>
+          <t>420683</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352411</t>
+          <t>401408</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>389139</t>
+          <t>440907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>721510</t>
+          <t>820277</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>689725</t>
+          <t>784875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>746430</t>
+          <t>852107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>145535</t>
+          <t>174095</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126562</t>
+          <t>148568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170616</t>
+          <t>198082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>130068</t>
+          <t>151552</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113795</t>
+          <t>134212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146709</t>
+          <t>169771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>275603</t>
+          <t>325647</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>249514</t>
+          <t>295133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>302240</t>
+          <t>356012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>541279</t>
+          <t>620972</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>541279</t>
+          <t>620972</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>541279</t>
+          <t>620972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1077618</t>
+          <t>1241809</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1077618</t>
+          <t>1241809</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1077618</t>
+          <t>1241809</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51143</t>
+          <t>52146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32888</t>
+          <t>36665</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>58567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75984</t>
+          <t>84687</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>70287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98901</t>
+          <t>101976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>430040</t>
+          <t>467138</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182530</t>
+          <t>441129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>603908</t>
+          <t>491498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>438498</t>
+          <t>476197</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>352217</t>
+          <t>455757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>469158</t>
+          <t>497811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>868538</t>
+          <t>943334</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>555796</t>
+          <t>909945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1046138</t>
+          <t>973954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>423116</t>
+          <t>194811</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237141</t>
+          <t>170732</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>686856</t>
+          <t>219427</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>231084</t>
+          <t>212731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200073</t>
+          <t>191968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>324122</t>
+          <t>233716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>654200</t>
+          <t>407542</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>459995</t>
+          <t>375607</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>986951</t>
+          <t>439778</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886908</t>
+          <t>699752</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886908</t>
+          <t>699752</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886908</t>
+          <t>699752</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735811</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735811</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735811</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1598723</t>
+          <t>1435563</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1598723</t>
+          <t>1435563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1598723</t>
+          <t>1435563</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42994</t>
+          <t>48536</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55860</t>
+          <t>60913</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>36436</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>27402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>45567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>74201</t>
+          <t>84973</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>71368</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89079</t>
+          <t>102556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>345044</t>
+          <t>372247</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>324937</t>
+          <t>349023</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367961</t>
+          <t>395757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>352962</t>
+          <t>391930</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>335640</t>
+          <t>374607</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>369807</t>
+          <t>411562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>698007</t>
+          <t>764177</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>668685</t>
+          <t>735596</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>725730</t>
+          <t>790660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>171175</t>
+          <t>186536</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151350</t>
+          <t>165653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191897</t>
+          <t>208563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>163094</t>
+          <t>179799</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146844</t>
+          <t>161880</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180215</t>
+          <t>196253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>334270</t>
+          <t>366335</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310167</t>
+          <t>338757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>365476</t>
+          <t>395066</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>559214</t>
+          <t>607320</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559214</t>
+          <t>607320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>559214</t>
+          <t>607320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547263</t>
+          <t>608165</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547263</t>
+          <t>608165</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547263</t>
+          <t>608165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1106477</t>
+          <t>1215485</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1106477</t>
+          <t>1215485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1106477</t>
+          <t>1215485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,102 +3005,102 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21461</t>
+          <t>23445</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>31981</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>25839</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>19378</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>33092</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>49284</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>39616</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>61127</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>22913</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>8174</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>37337</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>44373</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>22116</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>61301</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>237967</t>
+          <t>262691</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>223184</t>
+          <t>246020</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>251610</t>
+          <t>279340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>244633</t>
+          <t>264808</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104186</t>
+          <t>250842</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>375757</t>
+          <t>279425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>482600</t>
+          <t>527499</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246042</t>
+          <t>507366</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>619313</t>
+          <t>548559</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>107421</t>
+          <t>119496</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94758</t>
+          <t>105003</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123148</t>
+          <t>137387</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>338600</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>196658</t>
+          <t>132745</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>492283</t>
+          <t>160645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>446021</t>
+          <t>265760</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>295869</t>
+          <t>244662</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>694479</t>
+          <t>285968</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>366849</t>
+          <t>405632</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>366849</t>
+          <t>405632</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>366849</t>
+          <t>405632</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>606146</t>
+          <t>436910</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>606146</t>
+          <t>436910</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>606146</t>
+          <t>436910</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>972995</t>
+          <t>842542</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>972995</t>
+          <t>842542</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>972995</t>
+          <t>842542</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>25590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>24568</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>44901</t>
+          <t>49814</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36560</t>
+          <t>39462</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55150</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>175136</t>
+          <t>191826</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>161317</t>
+          <t>178878</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187605</t>
+          <t>207079</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>255730</t>
+          <t>278519</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>262486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>269563</t>
+          <t>294650</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>470344</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>411831</t>
+          <t>450157</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>451030</t>
+          <t>491719</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>99395</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78493</t>
+          <t>85397</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103234</t>
+          <t>112366</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>140968</t>
+          <t>153622</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>128175</t>
+          <t>137315</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>154519</t>
+          <t>169160</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>231298</t>
+          <t>253017</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>212535</t>
+          <t>233253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>249457</t>
+          <t>272184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>281577</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>281577</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>281577</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425488</t>
+          <t>464245</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425488</t>
+          <t>464245</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425488</t>
+          <t>464245</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>707064</t>
+          <t>773175</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>707064</t>
+          <t>773175</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>707064</t>
+          <t>773175</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>239080</t>
+          <t>273713</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>179667</t>
+          <t>233941</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>276971</t>
+          <t>310406</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>244195</t>
+          <t>281041</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>199428</t>
+          <t>251397</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>277190</t>
+          <t>313255</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>483276</t>
+          <t>554754</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>417732</t>
+          <t>502716</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>537790</t>
+          <t>603391</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2100566</t>
+          <t>2286401</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1627905</t>
+          <t>2222416</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2278571</t>
+          <t>2346394</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2237680</t>
+          <t>2411951</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1812225</t>
+          <t>2358902</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2403435</t>
+          <t>2463660</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4338246</t>
+          <t>4698353</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3717717</t>
+          <t>4616737</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4627011</t>
+          <t>4780572</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1114774</t>
+          <t>967040</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>919853</t>
+          <t>907373</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1629412</t>
+          <t>1031330</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1173237</t>
+          <t>1035210</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>997406</t>
+          <t>988178</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1655952</t>
+          <t>1083488</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2288011</t>
+          <t>2002250</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1974319</t>
+          <t>1929276</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2970747</t>
+          <t>2078546</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
